--- a/PsychoPy-online/fpjt_files/Testblock_audios.xlsx
+++ b/PsychoPy-online/fpjt_files/Testblock_audios.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/cdabb12e9f34f4c5/10_Paper/105_MIA/10_BAS_Collab/FPJT/PsychoPy-online/fpjt_files/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/cdabb12e9f34f4c5/10_Paper/105_MIA/03_Platform/FPJT/PsychoPy-local/fpjt_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13" documentId="8_{1EA5F3C9-EA77-44A6-B666-B13D04478163}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A9D0A3F1-9118-4939-A4A5-81F5B962C4A6}"/>
+  <xr:revisionPtr revIDLastSave="14" documentId="8_{1EA5F3C9-EA77-44A6-B666-B13D04478163}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{384F3645-77CB-4D46-9FD6-3CDD2FB85F27}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="14476" xr2:uid="{EBEDE55E-FD75-470A-971C-5C2DEC714033}"/>
+    <workbookView xWindow="35158" yWindow="109" windowWidth="26083" windowHeight="13829" xr2:uid="{EBEDE55E-FD75-470A-971C-5C2DEC714033}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -30,6 +30,9 @@
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -559,43 +562,43 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF2247A4-2AA4-42C9-9EA0-5EB54651944C}">
   <dimension ref="A1:AF8"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.19921875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.86328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.3984375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.19921875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.86328125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.86328125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.19921875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.86328125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.3984375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.9296875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.86328125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="11.86328125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="12.19921875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="11.3984375" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="12.19921875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="11.3984375" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="11.86328125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="12.19921875" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.86328125" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="12.19921875" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.19921875" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="11.3984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.25" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.25" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="11.875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="12.625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="12.25" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="11.375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="12.25" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11.375" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="11.875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="12.625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="12.25" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="12.625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.875" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="12.25" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12.625" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.25" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="11.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>41</v>
       </c>
@@ -693,7 +696,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>24</v>
       </c>
@@ -791,7 +794,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>25</v>
       </c>
@@ -889,7 +892,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>37</v>
       </c>
@@ -987,7 +990,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>33</v>
       </c>
@@ -1004,7 +1007,7 @@
         <v>36</v>
       </c>
       <c r="F5" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G5" t="s">
         <v>26</v>
@@ -1085,7 +1088,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.25">
       <c r="I6" t="s">
         <v>25</v>
       </c>
@@ -1159,7 +1162,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.25">
       <c r="Q7" t="s">
         <v>29</v>
       </c>
@@ -1209,7 +1212,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.25">
       <c r="Y8" t="s">
         <v>37</v>
       </c>
